--- a/testfile.xlsx
+++ b/testfile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MEMORIA VIRTUAL proyecto AC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6450e5a01e7561fa/Desktop/ONG_proyectopersonal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AF2033-D3EC-41D3-830F-26791EF9C2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{C4F157CD-BDF4-4F50-B590-0573EC3F5741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C840DEFE-0D5B-4E1B-AA98-397C0AD48120}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5DDCFEDA-1EA9-45FF-A05C-EDFD6D100B4A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{5DDCFEDA-1EA9-45FF-A05C-EDFD6D100B4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Contenedores" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Numero Contenedor</t>
   </si>
@@ -77,13 +77,49 @@
     <t>31/12/2024</t>
   </si>
   <si>
-    <t>Bici</t>
-  </si>
-  <si>
     <t>Ordenadores</t>
   </si>
   <si>
     <t>Comida</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Bicis</t>
+  </si>
+  <si>
+    <t>Ropa</t>
+  </si>
+  <si>
+    <t>Herramientas</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Costura</t>
+  </si>
+  <si>
+    <t>Material de costruccion</t>
+  </si>
+  <si>
+    <t>Articulos de casa</t>
+  </si>
+  <si>
+    <t>Juegos</t>
+  </si>
+  <si>
+    <t>Patines</t>
+  </si>
+  <si>
+    <t>Limpieza y higiene</t>
+  </si>
+  <si>
+    <t>Material escolar</t>
+  </si>
+  <si>
+    <t>Otro</t>
   </si>
 </sst>
 </file>
@@ -465,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7579DB9-B6F9-487C-A373-F22E2C05ACA1}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
@@ -473,7 +509,7 @@
     <col min="7" max="7" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,18 +523,52 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>401</v>
       </c>
@@ -520,8 +590,44 @@
       <c r="G2">
         <v>66</v>
       </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+      <c r="R2">
+        <v>5</v>
+      </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>402</v>
       </c>
@@ -543,8 +649,44 @@
       <c r="G3">
         <v>77</v>
       </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+      <c r="P3">
+        <v>5</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>5</v>
+      </c>
+      <c r="S3">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>403</v>
       </c>
@@ -566,8 +708,44 @@
       <c r="G4">
         <v>88</v>
       </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>405</v>
       </c>
@@ -589,8 +767,44 @@
       <c r="G5">
         <v>99</v>
       </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>406</v>
       </c>
@@ -612,8 +826,44 @@
       <c r="G6">
         <v>111</v>
       </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>410</v>
       </c>
@@ -634,6 +884,42 @@
       </c>
       <c r="G7">
         <v>122</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/testfile.xlsx
+++ b/testfile.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="14_{C4F157CD-BDF4-4F50-B590-0573EC3F5741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C840DEFE-0D5B-4E1B-AA98-397C0AD48120}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{5DDCFEDA-1EA9-45FF-A05C-EDFD6D100B4A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5DDCFEDA-1EA9-45FF-A05C-EDFD6D100B4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Contenedores" sheetId="1" r:id="rId1"/>
